--- a/docs/settlements_data_dictionary.xlsx
+++ b/docs/settlements_data_dictionary.xlsx
@@ -8,24 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seforallorg.sharepoint.com/Middle-Earth/Shared Documents/3. Team Folders/Policy/UIEP/1. Activities/H. Center of Excellence/5. Data &amp; Tools/IEP Cooling Component/MDG/AgCAP MDG - deploy folder/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="11_AD4DB114E441178AC67DF47D76D1C12A683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9F7BA36-F5F3-447F-9071-2C35249F452D}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="11_AD4DB114E441178AC67DF47D76D1C12A683EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC83CA9F-7C33-4E13-BA19-3DA65455E0E3}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settlements" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="142">
   <si>
     <t>Administrative &amp; Location</t>
   </si>
@@ -445,6 +457,12 @@
   </si>
   <si>
     <t>Number of fatalities due to conflict events within 10 km are calculated for last year available</t>
+  </si>
+  <si>
+    <t>Number of people living within the settlement boundary</t>
+  </si>
+  <si>
+    <t>Night lights intensity</t>
   </si>
 </sst>
 </file>
@@ -534,7 +552,102 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -644,12 +757,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FF1A474-0E52-4EB2-A212-0A220AF5D840}" name="Table1" displayName="Table1" ref="A1:C64" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FF1A474-0E52-4EB2-A212-0A220AF5D840}" name="Table1" displayName="Table1" ref="A1:C64" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:C64" xr:uid="{3FF1A474-0E52-4EB2-A212-0A220AF5D840}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{80DBAC68-1B35-4332-A2F9-5E3DA833597A}" name="Category" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{B59576C4-A5CA-49CB-A457-3918E71E2413}" name="Column name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{450AD135-6363-4DF1-9B34-8DCA36FEAC0E}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{80DBAC68-1B35-4332-A2F9-5E3DA833597A}" name="Category" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B59576C4-A5CA-49CB-A457-3918E71E2413}" name="Column name" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{450AD135-6363-4DF1-9B34-8DCA36FEAC0E}" name="Description" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3FAE68E-CB41-4E2C-982C-A472C0986127}" name="Table13" displayName="Table13" ref="A1:C64" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C64" xr:uid="{A3FAE68E-CB41-4E2C-982C-A472C0986127}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0D903F12-AC82-4DE0-84A2-EBA8F3E3242F}" name="Category" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D7E05B64-26EF-4429-B05F-9F52B67E0502}" name="Column name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{933693D2-42C3-4F5A-9E46-938360F09CF2}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1646,6 +1771,729 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629AF714-3B36-4087-B41F-2E43F5D6EBD2}">
+  <dimension ref="A1:C64"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="38.6" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="51.45" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="51.45" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="51.45" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="51.45" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="51.45" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="25.75" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="38.6" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="38.6" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="38.6" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1656,6 +2504,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Datetime xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <Yes_x002f_No xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">true</Yes_x002f_No>
+    <Date_x002f_Time xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <Date xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071561D1A5621A2498CEC3D8456AF0272" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="673ae7116fe741eba857aa140154d293">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xmlns:ns3="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d91f7a8935eb54ad5101523981e9c0e" ns2:_="" ns3:_="">
     <xsd:import namespace="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
@@ -1940,21 +2803,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Datetime xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <Yes_x002f_No xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">true</Yes_x002f_No>
-    <Date_x002f_Time xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <Date xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4736AFC0-EE16-47D8-A85B-C70E1E9C2AF2}">
   <ds:schemaRefs>
@@ -1964,6 +2812,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CA3573-F0A2-4321-A14E-5B173DE497C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="418c1687-f2b4-4c60-bff4-9f013a1b0e9b"/>
+    <ds:schemaRef ds:uri="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{278170EF-573D-4460-86B8-D68725969D0F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1980,15 +2839,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CA3573-F0A2-4321-A14E-5B173DE497C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="418c1687-f2b4-4c60-bff4-9f013a1b0e9b"/>
-    <ds:schemaRef ds:uri="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/settlements_data_dictionary.xlsx
+++ b/docs/settlements_data_dictionary.xlsx
@@ -2504,21 +2504,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Datetime xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <Yes_x002f_No xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">true</Yes_x002f_No>
-    <Date_x002f_Time xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <Date xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071561D1A5621A2498CEC3D8456AF0272" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="673ae7116fe741eba857aa140154d293">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xmlns:ns3="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d91f7a8935eb54ad5101523981e9c0e" ns2:_="" ns3:_="">
     <xsd:import namespace="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
@@ -2803,6 +2788,21 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Datetime xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <Yes_x002f_No xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b">true</Yes_x002f_No>
+    <Date_x002f_Time xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <Date xmlns="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4736AFC0-EE16-47D8-A85B-C70E1E9C2AF2}">
   <ds:schemaRefs>
@@ -2812,17 +2812,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CA3573-F0A2-4321-A14E-5B173DE497C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="418c1687-f2b4-4c60-bff4-9f013a1b0e9b"/>
-    <ds:schemaRef ds:uri="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{278170EF-573D-4460-86B8-D68725969D0F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2839,4 +2828,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CA3573-F0A2-4321-A14E-5B173DE497C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="418c1687-f2b4-4c60-bff4-9f013a1b0e9b"/>
+    <ds:schemaRef ds:uri="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/settlements_data_dictionary.xlsx
+++ b/docs/settlements_data_dictionary.xlsx
@@ -1558,11 +1558,15 @@
       <c r="A58" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>98</v>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Fishing Activity (Highest type)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Composite indicator of fishing activity, taken as the higher of the marine and inland sub-indices (0=lowest, 1=highest).</t>
+        </is>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -1572,8 +1576,10 @@
       <c r="B59" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>99</v>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Predominant fishing modality (marine or inland), based on whichever activity sub-index scores higher</t>
+        </is>
       </c>
     </row>
     <row r="60" spans="1:3" ht="25.75" x14ac:dyDescent="0.35">
